--- a/dirasakan(JANGAN DIHAPUS).xlsx
+++ b/dirasakan(JANGAN DIHAPUS).xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7FFF4F-CB27-4898-ACC9-BA2A00811A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803E51E5-30A3-43CB-97F2-647C3DE4B176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Tanggal</t>
   </si>
@@ -61,24 +56,14 @@
   </si>
   <si>
     <t>dirasakan di wilayah Mataram, Lombok Barat, Lombok Tengah, Badung, Gianyar, Denpasar II MMI</t>
-  </si>
-  <si>
-    <t>75 km Tenggara Kuta Selatan, Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah  Lombok Barat, Lombok Tengah, Kota Mataram III MMI, dan Denpasar II MMI</t>
-  </si>
-  <si>
-    <t>20:33:35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -111,12 +96,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,10 +414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -513,32 +496,6 @@
       </c>
       <c r="H3" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="3">
-        <v>45976</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4">
-        <v>-9.36</v>
-      </c>
-      <c r="D4" s="4">
-        <v>115.61</v>
-      </c>
-      <c r="E4" s="4">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
